--- a/healthcare_surveys/004_human_albumin_usage_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/004_human_albumin_usage_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cardiology'}</t>
+          <t>cardiology</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cardiology'}</t>
+          <t>Cardiology</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'dermatology'}</t>
+          <t>dermatology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Dermatology'}</t>
+          <t>Dermatology</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'emergency_medicine'}</t>
+          <t>emergency_medicine</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Emergency Medicine'}</t>
+          <t>Emergency Medicine</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'general_medicine'}</t>
+          <t>general_medicine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'General Medicine'}</t>
+          <t>General Medicine</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'neurology'}</t>
+          <t>neurology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Neurology'}</t>
+          <t>Neurology</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'oncology'}</t>
+          <t>oncology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Oncology'}</t>
+          <t>Oncology</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'radiology'}</t>
+          <t>radiology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Radiology'}</t>
+          <t>Radiology</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'surgery'}</t>
+          <t>surgery</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Surgery'}</t>
+          <t>Surgery</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'urology'}</t>
+          <t>urology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Urology'}</t>
+          <t>Urology</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cardiology'}</t>
+          <t>cardiology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cardiology'}</t>
+          <t>Cardiology</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'dermatology'}</t>
+          <t>dermatology</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Dermatology'}</t>
+          <t>Dermatology</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'emergency_medicine'}</t>
+          <t>emergency_medicine</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Emergency Medicine'}</t>
+          <t>Emergency Medicine</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'general_medicine'}</t>
+          <t>general_medicine</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'General Medicine'}</t>
+          <t>General Medicine</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'neurology'}</t>
+          <t>neurology</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Neurology'}</t>
+          <t>Neurology</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'oncology'}</t>
+          <t>oncology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Oncology'}</t>
+          <t>Oncology</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'radiology'}</t>
+          <t>radiology</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Radiology'}</t>
+          <t>Radiology</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'surgery'}</t>
+          <t>surgery</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Surgery'}</t>
+          <t>Surgery</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'urology'}</t>
+          <t>urology</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Urology'}</t>
+          <t>Urology</t>
         </is>
       </c>
     </row>
